--- a/Sheets/AWS-Zero-to-Hero-Sheet.xlsx
+++ b/Sheets/AWS-Zero-to-Hero-Sheet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8280"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="39">
   <si>
     <t>AWS Official Documentations
 https://docs.aws.amazon.com/</t>
@@ -446,14 +446,36 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">NACL - &gt; Subnets
-Security Groups(SG) -&gt; Instances
+      <t>NACL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> - &gt; Subnets
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Security Groups(SG)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> -&gt; Instances
 </t>
     </r>
     <r>
@@ -726,12 +748,19 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
         <b/>
-        <sz val="11"/>
+        <u/>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="Times New Roman"/>
         <charset val="134"/>
@@ -755,7 +784,26 @@
         <rFont val="Times New Roman"/>
         <charset val="134"/>
       </rPr>
-      <t>VPC</t>
+      <t xml:space="preserve">VPC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>with</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> Public-Private Subnet</t>
     </r>
     <r>
       <rPr>
@@ -793,11 +841,188 @@
         <rFont val="Times New Roman"/>
         <charset val="134"/>
       </rPr>
-      <t>Production Enviroment</t>
+      <t xml:space="preserve">Production Enviroment
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Practical understanding of</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 
+VPC Public-Private Architecture</t>
     </r>
   </si>
   <si>
     <t>Pending</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">* Auto Scaling Group: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">automatically adds, removes, and replaces servers.
+* </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Application Load Balancer: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>intelligently distributes user requests across those servers.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+* Bastion Host</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">: A Bastion Host (also called a Jump Server) is a secure administrative server used to access instances located in private subnets.
+* </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Target Group</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">: An AWS resource that defines and monitors the backend targets (such as EC2 instances) to which a load balancer forwards traffic.
+</t>
+    </r>
+  </si>
+  <si>
+    <t>https://docs.aws.amazon.com/vpc/latest/userguide/vpc-example-private-subnets-nat.html</t>
+  </si>
+  <si>
+    <t>Continued...</t>
+  </si>
+  <si>
+    <r>
+      <t>scp -i (Secure Copy Protocol)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> - Secruely copies content from one host to another </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ALB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> – Serves web traffic to private EC2
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Bastion Host</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> – Admin SSH/RDP access to private EC2
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>NAT Gateway</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> – Outbound internet access for private EC2</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -811,7 +1036,7 @@
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="180" formatCode="dd/mmm/yy"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1006,6 +1231,14 @@
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
@@ -1577,7 +1810,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1665,6 +1898,30 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2222,7 +2479,7 @@
       <c r="D13" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="13" t="s">
         <v>25</v>
       </c>
       <c r="F13" s="14">
@@ -2292,7 +2549,7 @@
       <c r="G17" s="27"/>
       <c r="H17" s="28"/>
     </row>
-    <row r="18" ht="51" customHeight="1" spans="1:7">
+    <row r="18" ht="183" customHeight="1" spans="1:7">
       <c r="A18" s="11">
         <v>7</v>
       </c>
@@ -2303,11 +2560,15 @@
       <c r="D18" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E18" s="11"/>
+      <c r="E18" s="13" t="s">
+        <v>34</v>
+      </c>
       <c r="F18" s="14">
-        <v>46010</v>
-      </c>
-      <c r="G18" s="12"/>
+        <v>46011</v>
+      </c>
+      <c r="G18" s="29" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="11"/>
@@ -2318,23 +2579,35 @@
       <c r="F19" s="11"/>
       <c r="G19" s="12"/>
     </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="11"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="12"/>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="11"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="12"/>
+    <row r="20" ht="37" customHeight="1" spans="1:7">
+      <c r="A20" s="30">
+        <v>7</v>
+      </c>
+      <c r="B20" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="F20" s="32">
+        <v>46024</v>
+      </c>
+      <c r="G20" s="33"/>
+    </row>
+    <row r="21" ht="75" customHeight="1" spans="1:7">
+      <c r="A21" s="34"/>
+      <c r="B21" s="35"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F21" s="36"/>
+      <c r="G21" s="37"/>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="11"/>
@@ -4416,14 +4689,20 @@
       <c r="G252" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="14">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A20:A21"/>
     <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B20:B21"/>
     <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C20:C21"/>
     <mergeCell ref="D6:D7"/>
+    <mergeCell ref="D20:D21"/>
     <mergeCell ref="F6:F7"/>
+    <mergeCell ref="F20:F21"/>
     <mergeCell ref="G6:G7"/>
+    <mergeCell ref="G20:G21"/>
     <mergeCell ref="H1:H1048576"/>
   </mergeCells>
   <hyperlinks>
@@ -4434,6 +4713,7 @@
     <hyperlink ref="G11" r:id="rId7" display="https://docs.aws.amazon.com/vpc/latest/userguide/what-is-amazon-vpc.html" tooltip="https://docs.aws.amazon.com/vpc/latest/userguide/what-is-amazon-vpc.html"/>
     <hyperlink ref="G13" r:id="rId8" display="https://www.geeksforgeeks.org/computer-networks/difference-between-security-group-and-network-acl-in-aws/"/>
     <hyperlink ref="G16" r:id="rId9" display="https://aws.amazon.com/documentation-overview/route53/"/>
+    <hyperlink ref="G18" r:id="rId10" display="https://docs.aws.amazon.com/vpc/latest/userguide/vpc-example-private-subnets-nat.html"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/Sheets/AWS-Zero-to-Hero-Sheet.xlsx
+++ b/Sheets/AWS-Zero-to-Hero-Sheet.xlsx
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="41">
   <si>
     <t>AWS Official Documentations
 https://docs.aws.amazon.com/</t>
@@ -230,13 +230,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
       <t xml:space="preserve">&lt;Ubuntu&gt; Command to access EC2 Instance: </t>
     </r>
     <r>
@@ -446,6 +439,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>NACL</t>
     </r>
     <r>
@@ -958,6 +958,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>scp -i (Secure Copy Protocol)</t>
     </r>
     <r>
@@ -972,6 +979,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>ALB</t>
     </r>
     <r>
@@ -1022,6 +1036,109 @@
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> – Outbound internet access for private EC2</t>
+    </r>
+  </si>
+  <si>
+    <t>10% Pending - 90% Done</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If an </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ASG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> has a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>minimum limit of 1 instance</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">, it will always keep </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>at least 1 instance running</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">; even if you </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>stop or terminate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> the instance, the ASG will automatically launch a </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>new one</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>.</t>
     </r>
   </si>
 </sst>
@@ -1029,14 +1146,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="180" formatCode="dd/mmm/yy"/>
+    <numFmt numFmtId="181" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1236,6 +1354,13 @@
       <b/>
       <u/>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
@@ -1810,7 +1935,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1899,12 +2024,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="180" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1922,6 +2041,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2254,7 +2376,7 @@
     <col min="2" max="2" width="35.5092592592593" style="3" customWidth="1"/>
     <col min="3" max="3" width="31.462962962963" style="3" customWidth="1"/>
     <col min="4" max="4" width="21.4444444444444" style="3" customWidth="1"/>
-    <col min="5" max="5" width="40.1481481481481" style="3" customWidth="1"/>
+    <col min="5" max="5" width="46.3888888888889" style="3" customWidth="1"/>
     <col min="6" max="6" width="14.8888888888889" style="3" customWidth="1"/>
     <col min="7" max="7" width="38.1203703703704" style="4" customWidth="1"/>
     <col min="8" max="8" width="8.88888888888889" style="5"/>
@@ -2580,34 +2702,34 @@
       <c r="G19" s="12"/>
     </row>
     <row r="20" ht="37" customHeight="1" spans="1:7">
-      <c r="A20" s="30">
+      <c r="A20" s="18">
         <v>7</v>
       </c>
-      <c r="B20" s="31" t="s">
+      <c r="B20" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30" t="s">
+      <c r="C20" s="18"/>
+      <c r="D20" s="18" t="s">
         <v>33</v>
       </c>
       <c r="E20" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F20" s="32">
+      <c r="F20" s="30">
         <v>46024</v>
       </c>
-      <c r="G20" s="33"/>
+      <c r="G20" s="31"/>
     </row>
     <row r="21" ht="75" customHeight="1" spans="1:7">
-      <c r="A21" s="34"/>
-      <c r="B21" s="35"/>
-      <c r="C21" s="34"/>
-      <c r="D21" s="34"/>
+      <c r="A21" s="32"/>
+      <c r="B21" s="33"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
       <c r="E21" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="F21" s="36"/>
-      <c r="G21" s="37"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="35"/>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="11"/>
@@ -2618,13 +2740,23 @@
       <c r="F22" s="11"/>
       <c r="G22" s="12"/>
     </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="11"/>
-      <c r="B23" s="11"/>
+    <row r="23" ht="61" customHeight="1" spans="1:7">
+      <c r="A23" s="11">
+        <v>7</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>36</v>
+      </c>
       <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
+      <c r="D23" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F23" s="36">
+        <v>46025</v>
+      </c>
       <c r="G23" s="12"/>
     </row>
     <row r="24" spans="1:7">

--- a/Sheets/AWS-Zero-to-Hero-Sheet.xlsx
+++ b/Sheets/AWS-Zero-to-Hero-Sheet.xlsx
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="41">
   <si>
     <t>AWS Official Documentations
 https://docs.aws.amazon.com/</t>
@@ -230,6 +230,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">&lt;Ubuntu&gt; Command to access EC2 Instance: </t>
     </r>
     <r>
@@ -1043,6 +1050,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">If an </t>
     </r>
     <r>
@@ -1351,16 +1364,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <u/>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <u/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
@@ -2765,12 +2778,18 @@
       <c r="C24" s="11"/>
       <c r="D24" s="11"/>
       <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
+      <c r="F24" s="36">
+        <v>46029</v>
+      </c>
       <c r="G24" s="12"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="11"/>
-      <c r="B25" s="11"/>
+      <c r="A25" s="11">
+        <v>7</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>36</v>
+      </c>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
       <c r="E25" s="11"/>
